--- a/public/templates/catalog-import-06.xlsx
+++ b/public/templates/catalog-import-06.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_填写说明" sheetId="1" r:id="Raaf883cba27e424d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_快速接头" sheetId="2" r:id="R5c298c62c46d4f3d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_字段字典" sheetId="3" r:id="R2da830cb28254b03"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_下拉选项" sheetId="4" r:id="R587241a91bc44889"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_填写说明" sheetId="1" r:id="R76e87c5479ed4926"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_快速接头" sheetId="2" r:id="R324367d1c10143ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_字段字典" sheetId="3" r:id="R87a4474cd8fc4566"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_下拉选项" sheetId="4" r:id="Re7a1163e713d4ec0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -78,7 +78,13 @@
     </x:fill>
   </x:fills>
   <x:borders count="1">
-    <x:border/>
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top/>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>

--- a/public/templates/catalog-import-06.xlsx
+++ b/public/templates/catalog-import-06.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_填写说明" sheetId="1" r:id="R76e87c5479ed4926"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_快速接头" sheetId="2" r:id="R324367d1c10143ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_字段字典" sheetId="3" r:id="R87a4474cd8fc4566"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_下拉选项" sheetId="4" r:id="Re7a1163e713d4ec0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_填写说明" sheetId="1" r:id="R4a6536cd59f5454e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_快速接头" sheetId="2" r:id="Rb73f822e08094f6f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_字段字典" sheetId="3" r:id="R5be54f54322941f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_下拉选项" sheetId="4" r:id="R469de10d553d4645"/>
   </x:sheets>
 </x:workbook>
 </file>
